--- a/tasks/finalpool/pw-notion-gform-survey-excel-word/groundtruth_workspace/Survey_Report.xlsx
+++ b/tasks/finalpool/pw-notion-gform-survey-excel-word/groundtruth_workspace/Survey_Report.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,26 +415,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Internal_Value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>External_Benchmark</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
@@ -457,32 +443,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Category A</t>
+          <t>1-on-1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Category B</t>
+          <t>All-Hands</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Strategy Review</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4" t="n">
         <v>90</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Team Standup</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D6" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -501,12 +535,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -519,7 +553,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -529,7 +563,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -543,16 +577,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
@@ -564,7 +598,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Review Category B</t>
+          <t>Review Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Review 1-on-1</t>
         </is>
       </c>
     </row>
